--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/PdDefaultManager001MTM.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/PdDefaultManager001MTM.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projectManager\company\zgbs3.0_tams\tams\tams-valuation-parent\tams-valuation\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13600" windowHeight="5990"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13596" windowHeight="5988"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>年份</t>
   </si>
@@ -35,82 +35,6 @@
   <si>
     <t>前瞻前年度边际PD%</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01:AAA+</t>
-  </si>
-  <si>
-    <t>02:AAA</t>
-  </si>
-  <si>
-    <t>03:AAA-</t>
-  </si>
-  <si>
-    <t>04:AA+</t>
-  </si>
-  <si>
-    <t>05:AA</t>
-  </si>
-  <si>
-    <t>06:AA-</t>
-  </si>
-  <si>
-    <t>07:A+</t>
-  </si>
-  <si>
-    <t>08:A</t>
-  </si>
-  <si>
-    <t>09:A-</t>
-  </si>
-  <si>
-    <t>10:BBB+</t>
-  </si>
-  <si>
-    <t>11:BBB</t>
-  </si>
-  <si>
-    <t>12:BBB-</t>
-  </si>
-  <si>
-    <t>13:BB+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:BB</t>
-  </si>
-  <si>
-    <t>15:BB-</t>
-  </si>
-  <si>
-    <t>16:B</t>
-  </si>
-  <si>
-    <t>17:CCC+</t>
-  </si>
-  <si>
-    <t>18:CCC</t>
-  </si>
-  <si>
-    <t>19:CCC-</t>
-  </si>
-  <si>
-    <t>20:CC+</t>
-  </si>
-  <si>
-    <t>21:CC</t>
-  </si>
-  <si>
-    <t>22:CC-</t>
-  </si>
-  <si>
-    <t>23:C</t>
-  </si>
-  <si>
-    <t>25:D</t>
-  </si>
-  <si>
-    <t>24:C-</t>
   </si>
 </sst>
 </file>
@@ -156,7 +80,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -164,6 +88,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,21 +373,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N43"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.90625" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" customWidth="1"/>
-    <col min="8" max="11" width="12.453125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.453125" customWidth="1"/>
-    <col min="13" max="13" width="12.90625" customWidth="1"/>
-    <col min="14" max="14" width="12.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.81640625" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="11" width="12.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="23.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -475,292 +402,221 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="2"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="2"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="2"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="2"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="2"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="1"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="2"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="2"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="2"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="2"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="2"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="2"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="2"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="2"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="4">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5">
       <formula1>"01:AAA+,02:AAA,03:AAA-,04:AA+,05:AA,06:AA-,07:A+,08:A,09:A-,13:BBB+,14:BBB,15:BBB-,17:BB,20:B,23:CCC,26:CC,29:C,31:D"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B43 B3:B13">
-      <formula1>"01:AAA+,02:AAA,03:AAA-,04:AA+,05:AA,06:AA-,07:A+,08:A,09:A-,10:BBB+,11:BBB,12:BBB-,13:BB+,14:BB,15:BB-,16:B,17:CCC+,18:CCC,19:CCC-,20:CC+,21:CC,22:CC-,23:C,24:C-,25:D"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
-      <formula1>"01:AAA+,02:AAA,03:AAA-,04:AA+,05:AA,06:AA-,07:A+,08:A,09:A-,10:BBB+,11:BBB,12:BBB-,13:BB+,14:BB,15:BB-,16:B,17:CCC+,18:CCC,19:CCC-,20:CC+,21:CC,22:CC-,23:C,24:C,25:D"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>"01:AAA+,02:AAA,03:AAA-,04:AA+,05:AA,06:AA-,07:A+,08:A,09:A-,10:BBB+,11:BBB,12:BBB-,13:BB+,14:BB,15:BB-,16:B,17:CCC+,18:CCC,19:CCC-,20:CC+,21:CC,22:CC-,23:C,24:C-,25:D"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B46">
+      <formula1>"01:AAA+,02:AAA,03:AAA-,04:AA+,05:AA,06:AA-,07:A+,08:A,09:A-,10:BBB+,11:BBB,12:BBB-,13:BB+,14:BB,15:BB-,16:B,17:CCC+,18:CCC,19:CCC-,20:CC+,21:CC,22:CC-,23:C+,24:C,25:C-,26:D"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
